--- a/assets/LargeScaleSubmissionTable.xlsx
+++ b/assets/LargeScaleSubmissionTable.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pporras\Documents\Documentation\IntAct\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hhe/Library/CloudStorage/Dropbox/pro/intact/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000D7623-0C48-A746-8170-F58EB31E764D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2910" yWindow="75" windowWidth="22035" windowHeight="8760"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="68800" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="5" r:id="rId1"/>
@@ -27,13 +28,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Philip Jones</author>
     <author>Pablo Porras Millan</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -41,12 +42,13 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Contact name for the data set.</t>
         </r>
       </text>
     </comment>
-    <comment ref="A4" authorId="0" shapeId="0">
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -54,12 +56,13 @@
             <sz val="8"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Mandatory name of an institution at which the named person can be found.</t>
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="1" shapeId="0">
+    <comment ref="A11" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -88,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="122">
   <si>
     <t>Publication Title</t>
   </si>
@@ -451,12 +454,15 @@
   </si>
   <si>
     <t xml:space="preserve">Use this example as a reference and just delete the example data and paste your on top once you have a clear idea on how to fill in the information. A detailed description of the fileds can be found in the "Instructions" spreadsheet. </t>
+  </si>
+  <si>
+    <t>To the best of my knowledge, the data being submitted are not subject to any restrictions that prohibit their open sharing and are submitted in compliance with applicable national and international access and benefit-sharing obligations, in accordance with the EMBL-EBI Terms of Use.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -604,6 +610,7 @@
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -615,6 +622,7 @@
       <sz val="8"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1102,23 +1110,8 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="12" xfId="42" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="42" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1136,13 +1129,43 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="12" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1220,7 +1243,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Line Callout 1 (Border and Accent Bar) 2"/>
+        <xdr:cNvPr id="3" name="Line Callout 1 (Border and Accent Bar) 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1305,6 +1334,11 @@
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="Line Callout 1 (Border and Accent Bar) 3">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
@@ -1412,6 +1446,11 @@
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="Line Callout 1 (Border and Accent Bar) 4">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
@@ -1508,7 +1547,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="Straight Connector 6"/>
+        <xdr:cNvPr id="7" name="Straight Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="4" idx="2"/>
         </xdr:cNvCxnSpPr>
@@ -1570,7 +1615,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Line Callout 1 (Border and Accent Bar) 14"/>
+        <xdr:cNvPr id="15" name="Line Callout 1 (Border and Accent Bar) 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1672,7 +1723,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="Line Callout 1 (Border and Accent Bar) 15"/>
+        <xdr:cNvPr id="16" name="Line Callout 1 (Border and Accent Bar) 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1755,7 +1812,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="Line Callout 1 (Border and Accent Bar) 16"/>
+        <xdr:cNvPr id="17" name="Line Callout 1 (Border and Accent Bar) 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1857,7 +1920,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="Line Callout 1 (Border and Accent Bar) 17"/>
+        <xdr:cNvPr id="18" name="Line Callout 1 (Border and Accent Bar) 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1959,7 +2028,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="Line Callout 1 (Border and Accent Bar) 18"/>
+        <xdr:cNvPr id="19" name="Line Callout 1 (Border and Accent Bar) 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2042,7 +2117,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="Line Callout 1 (Border and Accent Bar) 19"/>
+        <xdr:cNvPr id="20" name="Line Callout 1 (Border and Accent Bar) 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2125,7 +2206,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="Line Callout 1 (Border and Accent Bar) 20"/>
+        <xdr:cNvPr id="21" name="Line Callout 1 (Border and Accent Bar) 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2208,7 +2295,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Line Callout 1 (Border and Accent Bar) 21"/>
+        <xdr:cNvPr id="22" name="Line Callout 1 (Border and Accent Bar) 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2291,7 +2384,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Line Callout 1 (Border and Accent Bar) 13"/>
+        <xdr:cNvPr id="14" name="Line Callout 1 (Border and Accent Bar) 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2374,7 +2473,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Line Callout 1 (Border and Accent Bar) 22"/>
+        <xdr:cNvPr id="23" name="Line Callout 1 (Border and Accent Bar) 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2457,7 +2562,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="Line Callout 1 (Border and Accent Bar) 23"/>
+        <xdr:cNvPr id="24" name="Line Callout 1 (Border and Accent Bar) 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2559,7 +2670,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="Line Callout 1 (Border and Accent Bar) 24"/>
+        <xdr:cNvPr id="25" name="Line Callout 1 (Border and Accent Bar) 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2661,7 +2778,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="Line Callout 1 (Border and Accent Bar) 25"/>
+        <xdr:cNvPr id="26" name="Line Callout 1 (Border and Accent Bar) 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2763,7 +2886,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2914,7 +3043,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Introduction"/>
@@ -2953,10 +3082,27 @@
 </externalLink>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2994,9 +3140,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3031,7 +3177,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3066,7 +3212,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3239,135 +3385,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:D34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" customWidth="1"/>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C2" s="2"/>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C11" s="7" t="s">
         <v>116</v>
       </c>
       <c r="D11" s="6"/>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C12" s="8" t="s">
         <v>117</v>
       </c>
       <c r="D12" s="6"/>
     </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:4" x14ac:dyDescent="0.2">
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="21" t="s">
+    <row r="15" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C15" s="12" t="s">
         <v>32</v>
       </c>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="22" t="s">
+    <row r="16" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C16" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C17" s="22" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C17" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C18" s="22" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C18" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C19" s="23" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C19" s="14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="14" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C23" s="22" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C23" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C24" s="22" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C24" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C25" s="23" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C25" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C26" s="22" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C26" s="13" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C27" s="22" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C27" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C28" s="22" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C28" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C29" s="23" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C29" s="14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C30" s="23" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C30" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C31" s="22" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C31" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C32" s="23" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C32" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="23" t="s">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C33" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="24" t="s">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C34" s="15" t="s">
         <v>113</v>
       </c>
     </row>
@@ -3379,93 +3525,101 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="B3" s="24"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="14"/>
+      <c r="B4" s="24"/>
       <c r="D4" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="15"/>
+      <c r="B5" s="25"/>
       <c r="D5" s="8" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="17"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="B6" s="26"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="17"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="B7" s="26"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="19"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="B8" s="27"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="17"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="B9" s="26"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="17"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+      <c r="B10" s="26"/>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="24" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="64" x14ac:dyDescent="0.2">
+      <c r="A14" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3479,112 +3633,112 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5" customWidth="1"/>
+    <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" customWidth="1"/>
+    <col min="13" max="13" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5" customWidth="1"/>
     <col min="15" max="15" width="21" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="12" t="s">
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="9"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="21"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
@@ -3646,7 +3800,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -3702,7 +3856,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -3752,7 +3906,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3808,7 +3962,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -3858,7 +4012,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -3902,7 +4056,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -3943,7 +4097,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -3984,7 +4138,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -4025,7 +4179,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -4066,7 +4220,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>2</v>
       </c>
@@ -4107,7 +4261,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -4148,7 +4302,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>2</v>
       </c>
@@ -4189,7 +4343,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>2</v>
       </c>
@@ -4230,7 +4384,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>2</v>
       </c>
@@ -4271,7 +4425,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>2</v>
       </c>
@@ -4312,7 +4466,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>2</v>
       </c>
@@ -4353,7 +4507,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>2</v>
       </c>
@@ -4394,7 +4548,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>2</v>
       </c>
@@ -4435,7 +4589,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>2</v>
       </c>
@@ -4476,7 +4630,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>2</v>
       </c>
@@ -4517,7 +4671,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
@@ -4564,7 +4718,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>3</v>
       </c>
